--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92573258135</v>
+        <v>46157.93113739025</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93113739025</v>
+        <v>46157.93180747529</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93180747529</v>
+        <v>46157.93404678558</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93404678558</v>
+        <v>46157.93722732683</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93722732683</v>
+        <v>46158.2822062007</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2822062007</v>
+        <v>46158.29697353202</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29697353202</v>
+        <v>46158.29820137649</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29820137649</v>
+        <v>46158.33391593747</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33391593747</v>
+        <v>46158.36861412026</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36861412026</v>
+        <v>46158.37292043865</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
